--- a/Team-Data/2014-15/5-9-2014-15.xlsx
+++ b/Team-Data/2014-15/5-9-2014-15.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -784,7 +851,7 @@
         <v>30</v>
       </c>
       <c r="AS2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AT2" t="n">
         <v>28</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>5-9-2014-15</t>
+          <t>2015-05-09</t>
         </is>
       </c>
     </row>
@@ -933,7 +1000,7 @@
         <v>16</v>
       </c>
       <c r="AH3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AI3" t="n">
         <v>5</v>
@@ -960,7 +1027,7 @@
         <v>27</v>
       </c>
       <c r="AQ3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR3" t="n">
         <v>12</v>
@@ -984,10 +1051,10 @@
         <v>30</v>
       </c>
       <c r="AY3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA3" t="n">
         <v>26</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>5-9-2014-15</t>
+          <t>2015-05-09</t>
         </is>
       </c>
     </row>
@@ -1115,7 +1182,7 @@
         <v>18</v>
       </c>
       <c r="AH4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI4" t="n">
         <v>18</v>
@@ -1151,10 +1218,10 @@
         <v>17</v>
       </c>
       <c r="AT4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AU4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AV4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>5-9-2014-15</t>
+          <t>2015-05-09</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1394,7 @@
         <v>19</v>
       </c>
       <c r="AR5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AS5" t="n">
         <v>6</v>
@@ -1348,7 +1415,7 @@
         <v>7</v>
       </c>
       <c r="AY5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AZ5" t="n">
         <v>2</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>5-9-2014-15</t>
+          <t>2015-05-09</t>
         </is>
       </c>
     </row>
@@ -1473,13 +1540,13 @@
         <v>9</v>
       </c>
       <c r="AF6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AH6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AI6" t="n">
         <v>23</v>
@@ -1521,7 +1588,7 @@
         <v>14</v>
       </c>
       <c r="AV6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AW6" t="n">
         <v>28</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>5-9-2014-15</t>
+          <t>2015-05-09</t>
         </is>
       </c>
     </row>
@@ -1661,7 +1728,7 @@
         <v>7</v>
       </c>
       <c r="AH7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI7" t="n">
         <v>15</v>
@@ -1685,16 +1752,16 @@
         <v>9</v>
       </c>
       <c r="AP7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AR7" t="n">
         <v>11</v>
       </c>
       <c r="AS7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AT7" t="n">
         <v>18</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>5-9-2014-15</t>
+          <t>2015-05-09</t>
         </is>
       </c>
     </row>
@@ -1753,16 +1820,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E8" t="n">
         <v>50</v>
       </c>
       <c r="F8" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G8" t="n">
-        <v>0.617</v>
+        <v>0.61</v>
       </c>
       <c r="H8" t="n">
         <v>48.5</v>
@@ -1771,10 +1838,10 @@
         <v>39.7</v>
       </c>
       <c r="J8" t="n">
-        <v>85.90000000000001</v>
+        <v>85.8</v>
       </c>
       <c r="K8" t="n">
-        <v>0.462</v>
+        <v>0.463</v>
       </c>
       <c r="L8" t="n">
         <v>8.9</v>
@@ -1783,7 +1850,7 @@
         <v>25.4</v>
       </c>
       <c r="N8" t="n">
-        <v>0.351</v>
+        <v>0.352</v>
       </c>
       <c r="O8" t="n">
         <v>16.9</v>
@@ -1792,19 +1859,19 @@
         <v>22.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.751</v>
+        <v>0.752</v>
       </c>
       <c r="R8" t="n">
         <v>10.5</v>
       </c>
       <c r="S8" t="n">
-        <v>31.9</v>
+        <v>31.8</v>
       </c>
       <c r="T8" t="n">
-        <v>42.4</v>
+        <v>42.3</v>
       </c>
       <c r="U8" t="n">
-        <v>22.6</v>
+        <v>22.5</v>
       </c>
       <c r="V8" t="n">
         <v>13</v>
@@ -1822,22 +1889,22 @@
         <v>20</v>
       </c>
       <c r="AA8" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="AB8" t="n">
-        <v>105.3</v>
+        <v>105.2</v>
       </c>
       <c r="AC8" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AD8" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="AE8" t="n">
         <v>9</v>
       </c>
       <c r="AF8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG8" t="n">
         <v>9</v>
@@ -1849,7 +1916,7 @@
         <v>2</v>
       </c>
       <c r="AJ8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AK8" t="n">
         <v>5</v>
@@ -1870,16 +1937,16 @@
         <v>16</v>
       </c>
       <c r="AQ8" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AR8" t="n">
         <v>20</v>
       </c>
       <c r="AS8" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AT8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AU8" t="n">
         <v>8</v>
@@ -1891,7 +1958,7 @@
         <v>10</v>
       </c>
       <c r="AX8" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AY8" t="n">
         <v>4</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>5-9-2014-15</t>
+          <t>2015-05-09</t>
         </is>
       </c>
     </row>
@@ -2025,7 +2092,7 @@
         <v>24</v>
       </c>
       <c r="AH9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AI9" t="n">
         <v>13</v>
@@ -2058,7 +2125,7 @@
         <v>3</v>
       </c>
       <c r="AS9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AT9" t="n">
         <v>7</v>
@@ -2073,7 +2140,7 @@
         <v>14</v>
       </c>
       <c r="AX9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AY9" t="n">
         <v>29</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>5-9-2014-15</t>
+          <t>2015-05-09</t>
         </is>
       </c>
     </row>
@@ -2213,7 +2280,7 @@
         <v>20</v>
       </c>
       <c r="AJ10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AK10" t="n">
         <v>27</v>
@@ -2264,10 +2331,10 @@
         <v>7</v>
       </c>
       <c r="BA10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BB10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BC10" t="n">
         <v>20</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>5-9-2014-15</t>
+          <t>2015-05-09</t>
         </is>
       </c>
     </row>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>5-9-2014-15</t>
+          <t>2015-05-09</t>
         </is>
       </c>
     </row>
@@ -2481,16 +2548,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E12" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F12" t="n">
         <v>26</v>
       </c>
       <c r="G12" t="n">
-        <v>0.679</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="H12" t="n">
         <v>48.3</v>
@@ -2499,7 +2566,7 @@
         <v>37</v>
       </c>
       <c r="J12" t="n">
-        <v>83.40000000000001</v>
+        <v>83.3</v>
       </c>
       <c r="K12" t="n">
         <v>0.444</v>
@@ -2511,16 +2578,16 @@
         <v>32.7</v>
       </c>
       <c r="N12" t="n">
-        <v>0.347</v>
+        <v>0.348</v>
       </c>
       <c r="O12" t="n">
-        <v>18.4</v>
+        <v>18.6</v>
       </c>
       <c r="P12" t="n">
-        <v>25.7</v>
+        <v>26</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.716</v>
+        <v>0.715</v>
       </c>
       <c r="R12" t="n">
         <v>11.7</v>
@@ -2529,7 +2596,7 @@
         <v>32</v>
       </c>
       <c r="T12" t="n">
-        <v>43.6</v>
+        <v>43.7</v>
       </c>
       <c r="U12" t="n">
         <v>22.2</v>
@@ -2544,31 +2611,31 @@
         <v>5</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="Z12" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="AA12" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="AB12" t="n">
         <v>103.9</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="AE12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AF12" t="n">
         <v>3</v>
       </c>
       <c r="AG12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH12" t="n">
         <v>20</v>
@@ -2592,10 +2659,10 @@
         <v>14</v>
       </c>
       <c r="AO12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AP12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ12" t="n">
         <v>27</v>
@@ -2607,7 +2674,7 @@
         <v>18</v>
       </c>
       <c r="AT12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AU12" t="n">
         <v>9</v>
@@ -2622,7 +2689,7 @@
         <v>10</v>
       </c>
       <c r="AY12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AZ12" t="n">
         <v>27</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>5-9-2014-15</t>
+          <t>2015-05-09</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2847,7 @@
         <v>18</v>
       </c>
       <c r="AQ13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR13" t="n">
         <v>21</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>5-9-2014-15</t>
+          <t>2015-05-09</t>
         </is>
       </c>
     </row>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>5-9-2014-15</t>
+          <t>2015-05-09</t>
         </is>
       </c>
     </row>
@@ -3027,58 +3094,58 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E15" t="n">
         <v>21</v>
       </c>
       <c r="F15" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G15" t="n">
-        <v>0.259</v>
+        <v>0.256</v>
       </c>
       <c r="H15" t="n">
         <v>48.6</v>
       </c>
       <c r="I15" t="n">
-        <v>37.4</v>
+        <v>37.2</v>
       </c>
       <c r="J15" t="n">
-        <v>85.7</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>0.436</v>
+        <v>0.435</v>
       </c>
       <c r="L15" t="n">
         <v>6.5</v>
       </c>
       <c r="M15" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="N15" t="n">
         <v>0.344</v>
       </c>
       <c r="O15" t="n">
-        <v>17.3</v>
+        <v>17.5</v>
       </c>
       <c r="P15" t="n">
-        <v>23.4</v>
+        <v>23.6</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.739</v>
+        <v>0.741</v>
       </c>
       <c r="R15" t="n">
         <v>11.6</v>
       </c>
       <c r="S15" t="n">
-        <v>32.4</v>
+        <v>32.3</v>
       </c>
       <c r="T15" t="n">
-        <v>44</v>
+        <v>43.9</v>
       </c>
       <c r="U15" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="V15" t="n">
         <v>13.2</v>
@@ -3090,22 +3157,22 @@
         <v>4.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Z15" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="AA15" t="n">
-        <v>19.2</v>
+        <v>19.4</v>
       </c>
       <c r="AB15" t="n">
-        <v>98.59999999999999</v>
+        <v>98.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>-6.7</v>
+        <v>-6.8</v>
       </c>
       <c r="AD15" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="AE15" t="n">
         <v>27</v>
@@ -3141,7 +3208,7 @@
         <v>12</v>
       </c>
       <c r="AP15" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AQ15" t="n">
         <v>23</v>
@@ -3150,13 +3217,13 @@
         <v>8</v>
       </c>
       <c r="AS15" t="n">
+        <v>13</v>
+      </c>
+      <c r="AT15" t="n">
         <v>12</v>
       </c>
-      <c r="AT15" t="n">
-        <v>11</v>
-      </c>
       <c r="AU15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AV15" t="n">
         <v>5</v>
@@ -3165,19 +3232,19 @@
         <v>22</v>
       </c>
       <c r="AX15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AY15" t="n">
         <v>17</v>
       </c>
       <c r="AZ15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA15" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BB15" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BC15" t="n">
         <v>27</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>5-9-2014-15</t>
+          <t>2015-05-09</t>
         </is>
       </c>
     </row>
@@ -3290,7 +3357,7 @@
         <v>1</v>
       </c>
       <c r="AE16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF16" t="n">
         <v>5</v>
@@ -3308,7 +3375,7 @@
         <v>23</v>
       </c>
       <c r="AK16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AL16" t="n">
         <v>29</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>5-9-2014-15</t>
+          <t>2015-05-09</t>
         </is>
       </c>
     </row>
@@ -3493,7 +3560,7 @@
         <v>11</v>
       </c>
       <c r="AL17" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AM17" t="n">
         <v>19</v>
@@ -3529,7 +3596,7 @@
         <v>13</v>
       </c>
       <c r="AX17" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AY17" t="n">
         <v>8</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>5-9-2014-15</t>
+          <t>2015-05-09</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3730,7 @@
         <v>15</v>
       </c>
       <c r="AH18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI18" t="n">
         <v>16</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>5-9-2014-15</t>
+          <t>2015-05-09</t>
         </is>
       </c>
     </row>
@@ -3845,7 +3912,7 @@
         <v>30</v>
       </c>
       <c r="AH19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI19" t="n">
         <v>25</v>
@@ -3869,7 +3936,7 @@
         <v>2</v>
       </c>
       <c r="AP19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ19" t="n">
         <v>6</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>5-9-2014-15</t>
+          <t>2015-05-09</t>
         </is>
       </c>
     </row>
@@ -3937,16 +4004,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E20" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F20" t="n">
         <v>37</v>
       </c>
       <c r="G20" t="n">
-        <v>0.543</v>
+        <v>0.549</v>
       </c>
       <c r="H20" t="n">
         <v>48.2</v>
@@ -3955,37 +4022,37 @@
         <v>37.9</v>
       </c>
       <c r="J20" t="n">
-        <v>82.59999999999999</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>0.458</v>
+        <v>0.457</v>
       </c>
       <c r="L20" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="M20" t="n">
         <v>19.3</v>
       </c>
       <c r="N20" t="n">
-        <v>0.372</v>
+        <v>0.37</v>
       </c>
       <c r="O20" t="n">
         <v>16.4</v>
       </c>
       <c r="P20" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.756</v>
+        <v>0.751</v>
       </c>
       <c r="R20" t="n">
-        <v>11.3</v>
+        <v>11.5</v>
       </c>
       <c r="S20" t="n">
-        <v>31.9</v>
+        <v>32</v>
       </c>
       <c r="T20" t="n">
-        <v>43.2</v>
+        <v>43.5</v>
       </c>
       <c r="U20" t="n">
         <v>22</v>
@@ -3997,7 +4064,7 @@
         <v>6.7</v>
       </c>
       <c r="X20" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="Y20" t="n">
         <v>5.8</v>
@@ -4006,37 +4073,37 @@
         <v>18.7</v>
       </c>
       <c r="AA20" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="AB20" t="n">
-        <v>99.3</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="AD20" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="AE20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AF20" t="n">
         <v>13</v>
       </c>
       <c r="AG20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH20" t="n">
         <v>23</v>
       </c>
       <c r="AI20" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AJ20" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AK20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AL20" t="n">
         <v>19</v>
@@ -4054,13 +4121,13 @@
         <v>20</v>
       </c>
       <c r="AQ20" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AR20" t="n">
         <v>10</v>
       </c>
       <c r="AS20" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AT20" t="n">
         <v>16</v>
@@ -4072,7 +4139,7 @@
         <v>6</v>
       </c>
       <c r="AW20" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AX20" t="n">
         <v>1</v>
@@ -4090,7 +4157,7 @@
         <v>16</v>
       </c>
       <c r="BC20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>5-9-2014-15</t>
+          <t>2015-05-09</t>
         </is>
       </c>
     </row>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>5-9-2014-15</t>
+          <t>2015-05-09</t>
         </is>
       </c>
     </row>
@@ -4412,13 +4479,13 @@
         <v>23</v>
       </c>
       <c r="AO22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AP22" t="n">
         <v>6</v>
       </c>
       <c r="AQ22" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR22" t="n">
         <v>1</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>5-9-2014-15</t>
+          <t>2015-05-09</t>
         </is>
       </c>
     </row>
@@ -4483,34 +4550,34 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E23" t="n">
         <v>25</v>
       </c>
       <c r="F23" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G23" t="n">
-        <v>0.309</v>
+        <v>0.305</v>
       </c>
       <c r="H23" t="n">
         <v>48.2</v>
       </c>
       <c r="I23" t="n">
-        <v>37.6</v>
+        <v>37.5</v>
       </c>
       <c r="J23" t="n">
         <v>82.8</v>
       </c>
       <c r="K23" t="n">
-        <v>0.454</v>
+        <v>0.453</v>
       </c>
       <c r="L23" t="n">
         <v>6.8</v>
       </c>
       <c r="M23" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="N23" t="n">
         <v>0.347</v>
@@ -4528,13 +4595,13 @@
         <v>10</v>
       </c>
       <c r="S23" t="n">
-        <v>31.7</v>
+        <v>31.8</v>
       </c>
       <c r="T23" t="n">
-        <v>41.6</v>
+        <v>41.8</v>
       </c>
       <c r="U23" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="V23" t="n">
         <v>14.9</v>
@@ -4546,7 +4613,7 @@
         <v>3.8</v>
       </c>
       <c r="Y23" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="Z23" t="n">
         <v>20.9</v>
@@ -4555,13 +4622,13 @@
         <v>17.9</v>
       </c>
       <c r="AB23" t="n">
-        <v>95.8</v>
+        <v>95.7</v>
       </c>
       <c r="AC23" t="n">
-        <v>-5.6</v>
+        <v>-5.7</v>
       </c>
       <c r="AD23" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="AE23" t="n">
         <v>26</v>
@@ -4579,13 +4646,13 @@
         <v>17</v>
       </c>
       <c r="AJ23" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AK23" t="n">
         <v>14</v>
       </c>
       <c r="AL23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AM23" t="n">
         <v>22</v>
@@ -4603,7 +4670,7 @@
         <v>25</v>
       </c>
       <c r="AR23" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AS23" t="n">
         <v>24</v>
@@ -4624,10 +4691,10 @@
         <v>29</v>
       </c>
       <c r="AY23" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AZ23" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BA23" t="n">
         <v>30</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>5-9-2014-15</t>
+          <t>2015-05-09</t>
         </is>
       </c>
     </row>
@@ -4755,13 +4822,13 @@
         <v>28</v>
       </c>
       <c r="AH24" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI24" t="n">
         <v>30</v>
       </c>
       <c r="AJ24" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK24" t="n">
         <v>30</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>5-9-2014-15</t>
+          <t>2015-05-09</t>
         </is>
       </c>
     </row>
@@ -4937,13 +5004,13 @@
         <v>17</v>
       </c>
       <c r="AH25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AI25" t="n">
         <v>7</v>
       </c>
       <c r="AJ25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AK25" t="n">
         <v>15</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>5-9-2014-15</t>
+          <t>2015-05-09</t>
         </is>
       </c>
     </row>
@@ -5167,7 +5234,7 @@
         <v>27</v>
       </c>
       <c r="AX26" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AY26" t="n">
         <v>3</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>5-9-2014-15</t>
+          <t>2015-05-09</t>
         </is>
       </c>
     </row>
@@ -5346,7 +5413,7 @@
         <v>27</v>
       </c>
       <c r="AW27" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AX27" t="n">
         <v>28</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>5-9-2014-15</t>
+          <t>2015-05-09</t>
         </is>
       </c>
     </row>
@@ -5393,16 +5460,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E28" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F28" t="n">
         <v>27</v>
       </c>
       <c r="G28" t="n">
-        <v>0.667</v>
+        <v>0.671</v>
       </c>
       <c r="H28" t="n">
         <v>48.7</v>
@@ -5411,25 +5478,25 @@
         <v>39.1</v>
       </c>
       <c r="J28" t="n">
-        <v>83.8</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>0.467</v>
+        <v>0.468</v>
       </c>
       <c r="L28" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M28" t="n">
         <v>22.5</v>
       </c>
       <c r="N28" t="n">
-        <v>0.364</v>
+        <v>0.367</v>
       </c>
       <c r="O28" t="n">
         <v>16.7</v>
       </c>
       <c r="P28" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="Q28" t="n">
         <v>0.78</v>
@@ -5438,16 +5505,16 @@
         <v>9.800000000000001</v>
       </c>
       <c r="S28" t="n">
-        <v>33.9</v>
+        <v>33.8</v>
       </c>
       <c r="T28" t="n">
-        <v>43.7</v>
+        <v>43.6</v>
       </c>
       <c r="U28" t="n">
         <v>24.4</v>
       </c>
       <c r="V28" t="n">
-        <v>13.9</v>
+        <v>14</v>
       </c>
       <c r="W28" t="n">
         <v>8</v>
@@ -5468,19 +5535,19 @@
         <v>103.2</v>
       </c>
       <c r="AC28" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="AD28" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="AE28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF28" t="n">
         <v>5</v>
       </c>
       <c r="AG28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AH28" t="n">
         <v>1</v>
@@ -5507,7 +5574,7 @@
         <v>17</v>
       </c>
       <c r="AP28" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ28" t="n">
         <v>4</v>
@@ -5519,13 +5586,13 @@
         <v>8</v>
       </c>
       <c r="AT28" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AU28" t="n">
         <v>5</v>
       </c>
       <c r="AV28" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AW28" t="n">
         <v>11</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>5-9-2014-15</t>
+          <t>2015-05-09</t>
         </is>
       </c>
     </row>
@@ -5719,7 +5786,7 @@
         <v>19</v>
       </c>
       <c r="AZ29" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA29" t="n">
         <v>13</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>5-9-2014-15</t>
+          <t>2015-05-09</t>
         </is>
       </c>
     </row>
@@ -5871,7 +5938,7 @@
         <v>14</v>
       </c>
       <c r="AP30" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ30" t="n">
         <v>26</v>
@@ -5880,10 +5947,10 @@
         <v>4</v>
       </c>
       <c r="AS30" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AT30" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AU30" t="n">
         <v>29</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>5-9-2014-15</t>
+          <t>2015-05-09</t>
         </is>
       </c>
     </row>
@@ -6029,13 +6096,13 @@
         <v>12</v>
       </c>
       <c r="AH31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI31" t="n">
         <v>9</v>
       </c>
       <c r="AJ31" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK31" t="n">
         <v>6</v>
@@ -6053,7 +6120,7 @@
         <v>25</v>
       </c>
       <c r="AP31" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AQ31" t="n">
         <v>21</v>
@@ -6089,10 +6156,10 @@
         <v>21</v>
       </c>
       <c r="BB31" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BC31" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BD31" t="n">
         <v>10</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>5-9-2014-15</t>
+          <t>2015-05-09</t>
         </is>
       </c>
     </row>
